--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0002T0006Z000C1N33_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0002T0006Z000C1N33_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>63.39720645562591</v>
+        <v>10.30204604903921</v>
       </c>
       <c r="D2" t="n">
-        <v>63.72501828141554</v>
+        <v>10.35531547073002</v>
       </c>
       <c r="E2" t="n">
-        <v>17.18637932883084</v>
+        <v>2.79278664093501</v>
       </c>
       <c r="F2" t="n">
-        <v>18.08825099767408</v>
+        <v>2.939340787122038</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>58.99892396749463</v>
+        <v>9.587325144717877</v>
       </c>
       <c r="D3" t="n">
-        <v>59.15999088215607</v>
+        <v>9.613498518350362</v>
       </c>
       <c r="E3" t="n">
-        <v>17.18637932883084</v>
+        <v>2.79278664093501</v>
       </c>
       <c r="F3" t="n">
-        <v>18.08825099767408</v>
+        <v>2.939340787122038</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>58.72976155535769</v>
+        <v>9.543586252745625</v>
       </c>
       <c r="D4" t="n">
-        <v>59.04562665754173</v>
+        <v>9.594914331850532</v>
       </c>
       <c r="E4" t="n">
-        <v>17.18637932883084</v>
+        <v>2.79278664093501</v>
       </c>
       <c r="F4" t="n">
-        <v>18.08825099767408</v>
+        <v>2.939340787122038</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>70.86705348673813</v>
+        <v>11.51589619159495</v>
       </c>
       <c r="D5" t="n">
-        <v>70.85544768316878</v>
+        <v>11.51401024851493</v>
       </c>
       <c r="E5" t="n">
-        <v>17.18637932883084</v>
+        <v>2.79278664093501</v>
       </c>
       <c r="F5" t="n">
-        <v>18.08825099767408</v>
+        <v>2.939340787122038</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>54.57535091292191</v>
+        <v>8.86849452334981</v>
       </c>
       <c r="D6" t="n">
-        <v>54.80497261096951</v>
+        <v>8.905808049282545</v>
       </c>
       <c r="E6" t="n">
-        <v>17.18637932883084</v>
+        <v>2.79278664093501</v>
       </c>
       <c r="F6" t="n">
-        <v>18.08825099767408</v>
+        <v>2.939340787122038</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>63.99497238154108</v>
+        <v>10.39918301200043</v>
       </c>
       <c r="D7" t="n">
-        <v>64.36377488724922</v>
+        <v>10.459113419178</v>
       </c>
       <c r="E7" t="n">
-        <v>17.18637932883084</v>
+        <v>2.79278664093501</v>
       </c>
       <c r="F7" t="n">
-        <v>18.08825099767408</v>
+        <v>2.939340787122038</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>72.98057967927147</v>
+        <v>11.85934419788162</v>
       </c>
       <c r="D8" t="n">
-        <v>73.36974530242695</v>
+        <v>11.92258361164438</v>
       </c>
       <c r="E8" t="n">
-        <v>17.18637932883084</v>
+        <v>2.79278664093501</v>
       </c>
       <c r="F8" t="n">
-        <v>18.08825099767408</v>
+        <v>2.939340787122038</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>75.38918305255173</v>
+        <v>12.25074224603966</v>
       </c>
       <c r="D9" t="n">
-        <v>75.7722501986857</v>
+        <v>12.31299065728643</v>
       </c>
       <c r="E9" t="n">
-        <v>17.18637932883084</v>
+        <v>2.79278664093501</v>
       </c>
       <c r="F9" t="n">
-        <v>18.08825099767408</v>
+        <v>2.939340787122038</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>31.79421878684946</v>
+        <v>5.166560552863038</v>
       </c>
       <c r="D10" t="n">
-        <v>32.14397066237948</v>
+        <v>5.223395232636665</v>
       </c>
       <c r="E10" t="n">
-        <v>17.18637932883084</v>
+        <v>2.79278664093501</v>
       </c>
       <c r="F10" t="n">
-        <v>18.08825099767408</v>
+        <v>2.939340787122038</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>57.47046877857974</v>
+        <v>9.338951176519208</v>
       </c>
       <c r="D11" t="n">
-        <v>54.20876271876205</v>
+        <v>8.808923941798833</v>
       </c>
       <c r="E11" t="n">
-        <v>17.18637932883084</v>
+        <v>2.79278664093501</v>
       </c>
       <c r="F11" t="n">
-        <v>18.08825099767408</v>
+        <v>2.939340787122038</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>45.12975762760863</v>
+        <v>7.333585614486402</v>
       </c>
       <c r="D12" t="n">
-        <v>41.49801307484466</v>
+        <v>6.743427124662258</v>
       </c>
       <c r="E12" t="n">
-        <v>17.18637932883084</v>
+        <v>2.79278664093501</v>
       </c>
       <c r="F12" t="n">
-        <v>18.08825099767408</v>
+        <v>2.939340787122038</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>29.09402636143964</v>
+        <v>4.727779283733942</v>
       </c>
       <c r="D13" t="n">
-        <v>29.12129837238863</v>
+        <v>4.732210985513152</v>
       </c>
       <c r="E13" t="n">
-        <v>17.18637932883084</v>
+        <v>2.79278664093501</v>
       </c>
       <c r="F13" t="n">
-        <v>18.08825099767408</v>
+        <v>2.939340787122038</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>42.42851097140446</v>
+        <v>6.894633032853226</v>
       </c>
       <c r="D14" t="n">
-        <v>42.03953182061019</v>
+        <v>6.831423920849155</v>
       </c>
       <c r="E14" t="n">
-        <v>17.18637932883084</v>
+        <v>2.79278664093501</v>
       </c>
       <c r="F14" t="n">
-        <v>18.08825099767408</v>
+        <v>2.939340787122038</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>12.01507431468227</v>
+        <v>1.952449576135869</v>
       </c>
       <c r="D15" t="n">
-        <v>7.539004512176767</v>
+        <v>1.225088233228725</v>
       </c>
       <c r="E15" t="n">
-        <v>17.18637932883084</v>
+        <v>2.79278664093501</v>
       </c>
       <c r="F15" t="n">
-        <v>18.08825099767408</v>
+        <v>2.939340787122038</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>57.00151405121644</v>
+        <v>9.262746033322673</v>
       </c>
       <c r="D16" t="n">
-        <v>56.884277076133</v>
+        <v>9.243695024871613</v>
       </c>
       <c r="E16" t="n">
-        <v>17.18637932883084</v>
+        <v>2.79278664093501</v>
       </c>
       <c r="F16" t="n">
-        <v>18.08825099767408</v>
+        <v>2.939340787122038</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
